--- a/M-Project/M-Project_CED26/ced26_26_pattern.xlsx
+++ b/M-Project/M-Project_CED26/ced26_26_pattern.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\M-Project\M-Project_CED26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67125DEB-B33F-453E-9AB6-BB8E49ED00AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA989E4-E17C-483C-8712-3718D8B11633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="6075" windowWidth="29040" windowHeight="15720" xr2:uid="{E628082B-4EDE-4ED3-AF68-8213987AFF61}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{E628082B-4EDE-4ED3-AF68-8213987AFF61}"/>
   </bookViews>
   <sheets>
     <sheet name="Pulse Wave" sheetId="1" r:id="rId1"/>
@@ -130,11 +130,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -147,9 +147,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -501,29 +498,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB27C50F-0D07-43B2-8023-7E564C4A7FAF}">
-  <dimension ref="B2:DO60"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="B2:DO58"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5625" customWidth="1"/>
-    <col min="2" max="2" width="3.9375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="2" max="2" width="3.9140625" bestFit="1" customWidth="1"/>
     <col min="3" max="28" width="3" customWidth="1"/>
-    <col min="29" max="29" width="3.125" customWidth="1"/>
+    <col min="29" max="29" width="3.08203125" customWidth="1"/>
     <col min="30" max="31" width="9" customWidth="1"/>
-    <col min="32" max="32" width="3.9375" style="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="58" width="3" style="6" customWidth="1"/>
-    <col min="59" max="59" width="3.125" customWidth="1"/>
-    <col min="61" max="61" width="9" style="6"/>
-    <col min="62" max="62" width="3.9375" style="6" bestFit="1" customWidth="1"/>
-    <col min="63" max="88" width="3" style="6" customWidth="1"/>
-    <col min="89" max="89" width="3.125" style="6" customWidth="1"/>
-    <col min="90" max="91" width="9" style="6"/>
-    <col min="92" max="92" width="3.9375" style="6" bestFit="1" customWidth="1"/>
-    <col min="93" max="118" width="3" style="6" customWidth="1"/>
-    <col min="119" max="119" width="3.125" style="6" customWidth="1"/>
+    <col min="32" max="32" width="3.9140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="58" width="3" customWidth="1"/>
+    <col min="59" max="59" width="3.08203125" customWidth="1"/>
+    <col min="61" max="61" width="9"/>
+    <col min="62" max="62" width="3.9140625" bestFit="1" customWidth="1"/>
+    <col min="63" max="88" width="3" customWidth="1"/>
+    <col min="89" max="89" width="3.08203125" customWidth="1"/>
+    <col min="90" max="91" width="9"/>
+    <col min="92" max="92" width="3.9140625" bestFit="1" customWidth="1"/>
+    <col min="93" max="118" width="3" customWidth="1"/>
+    <col min="119" max="119" width="3.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:119" x14ac:dyDescent="0.6">
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="2:119" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2">
@@ -604,7 +601,7 @@
       <c r="AB2">
         <v>25</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AF2" t="s">
         <v>0</v>
       </c>
       <c r="AG2">
@@ -685,7 +682,7 @@
       <c r="BF2">
         <v>25</v>
       </c>
-      <c r="BJ2" s="6" t="s">
+      <c r="BJ2" t="s">
         <v>0</v>
       </c>
       <c r="BK2">
@@ -766,8 +763,7 @@
       <c r="CJ2">
         <v>25</v>
       </c>
-      <c r="CK2"/>
-      <c r="CN2" s="6" t="s">
+      <c r="CN2" t="s">
         <v>0</v>
       </c>
       <c r="CO2">
@@ -848,9 +844,8 @@
       <c r="DN2">
         <v>25</v>
       </c>
-      <c r="DO2"/>
     </row>
-    <row r="3" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B3">
         <v>0</v>
       </c>
@@ -980,7 +975,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B4">
         <v>1</v>
       </c>
@@ -1081,36 +1076,36 @@
         <v>1</v>
       </c>
       <c r="CO4" s="1"/>
-      <c r="CP4" s="7"/>
+      <c r="CP4" s="6"/>
       <c r="CQ4" s="1"/>
-      <c r="CR4" s="7"/>
+      <c r="CR4" s="6"/>
       <c r="CS4" s="1"/>
-      <c r="CT4" s="7"/>
+      <c r="CT4" s="6"/>
       <c r="CU4" s="1"/>
-      <c r="CV4" s="7"/>
+      <c r="CV4" s="6"/>
       <c r="CW4" s="1"/>
-      <c r="CX4" s="7"/>
+      <c r="CX4" s="6"/>
       <c r="CY4" s="1"/>
-      <c r="CZ4" s="7"/>
+      <c r="CZ4" s="6"/>
       <c r="DA4" s="1"/>
-      <c r="DB4" s="7"/>
+      <c r="DB4" s="6"/>
       <c r="DC4" s="1"/>
-      <c r="DD4" s="7"/>
+      <c r="DD4" s="6"/>
       <c r="DE4" s="1"/>
-      <c r="DF4" s="7"/>
+      <c r="DF4" s="6"/>
       <c r="DG4" s="1"/>
-      <c r="DH4" s="7"/>
+      <c r="DH4" s="6"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="7"/>
+      <c r="DJ4" s="6"/>
       <c r="DK4" s="1"/>
-      <c r="DL4" s="7"/>
+      <c r="DL4" s="6"/>
       <c r="DM4" s="1"/>
-      <c r="DN4" s="7"/>
+      <c r="DN4" s="6"/>
       <c r="DO4">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B5">
         <v>2</v>
       </c>
@@ -1240,7 +1235,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B6">
         <v>3</v>
       </c>
@@ -1341,36 +1336,36 @@
         <v>3</v>
       </c>
       <c r="CO6" s="1"/>
-      <c r="CP6" s="7"/>
+      <c r="CP6" s="6"/>
       <c r="CQ6" s="1"/>
-      <c r="CR6" s="7"/>
+      <c r="CR6" s="6"/>
       <c r="CS6" s="1"/>
-      <c r="CT6" s="7"/>
+      <c r="CT6" s="6"/>
       <c r="CU6" s="1"/>
-      <c r="CV6" s="7"/>
+      <c r="CV6" s="6"/>
       <c r="CW6" s="1"/>
-      <c r="CX6" s="7"/>
+      <c r="CX6" s="6"/>
       <c r="CY6" s="1"/>
-      <c r="CZ6" s="7"/>
+      <c r="CZ6" s="6"/>
       <c r="DA6" s="1"/>
-      <c r="DB6" s="7"/>
+      <c r="DB6" s="6"/>
       <c r="DC6" s="1"/>
-      <c r="DD6" s="7"/>
+      <c r="DD6" s="6"/>
       <c r="DE6" s="1"/>
-      <c r="DF6" s="7"/>
+      <c r="DF6" s="6"/>
       <c r="DG6" s="1"/>
-      <c r="DH6" s="7"/>
+      <c r="DH6" s="6"/>
       <c r="DI6" s="1"/>
-      <c r="DJ6" s="7"/>
+      <c r="DJ6" s="6"/>
       <c r="DK6" s="1"/>
-      <c r="DL6" s="7"/>
+      <c r="DL6" s="6"/>
       <c r="DM6" s="1"/>
-      <c r="DN6" s="7"/>
+      <c r="DN6" s="6"/>
       <c r="DO6">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B7">
         <v>4</v>
       </c>
@@ -1410,24 +1405,24 @@
       <c r="AH7" s="4"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="2"/>
-      <c r="AK7" s="7"/>
-      <c r="AL7" s="7"/>
-      <c r="AM7" s="7"/>
-      <c r="AN7" s="7"/>
-      <c r="AO7" s="7"/>
-      <c r="AP7" s="7"/>
-      <c r="AQ7" s="7"/>
-      <c r="AR7" s="7"/>
-      <c r="AS7" s="7"/>
-      <c r="AT7" s="7"/>
-      <c r="AU7" s="7"/>
-      <c r="AV7" s="7"/>
-      <c r="AW7" s="7"/>
-      <c r="AX7" s="7"/>
-      <c r="AY7" s="7"/>
-      <c r="AZ7" s="7"/>
-      <c r="BA7" s="7"/>
-      <c r="BB7" s="7"/>
+      <c r="AK7" s="6"/>
+      <c r="AL7" s="6"/>
+      <c r="AM7" s="6"/>
+      <c r="AN7" s="6"/>
+      <c r="AO7" s="6"/>
+      <c r="AP7" s="6"/>
+      <c r="AQ7" s="6"/>
+      <c r="AR7" s="6"/>
+      <c r="AS7" s="6"/>
+      <c r="AT7" s="6"/>
+      <c r="AU7" s="6"/>
+      <c r="AV7" s="6"/>
+      <c r="AW7" s="6"/>
+      <c r="AX7" s="6"/>
+      <c r="AY7" s="6"/>
+      <c r="AZ7" s="6"/>
+      <c r="BA7" s="6"/>
+      <c r="BB7" s="6"/>
       <c r="BC7" s="2"/>
       <c r="BD7" s="3"/>
       <c r="BE7" s="4"/>
@@ -1500,7 +1495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B8">
         <v>5</v>
       </c>
@@ -1540,7 +1535,7 @@
       <c r="AH8" s="4"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="2"/>
-      <c r="AK8" s="7"/>
+      <c r="AK8" s="6"/>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="1"/>
@@ -1557,7 +1552,7 @@
       <c r="AY8" s="1"/>
       <c r="AZ8" s="1"/>
       <c r="BA8" s="1"/>
-      <c r="BB8" s="7"/>
+      <c r="BB8" s="6"/>
       <c r="BC8" s="2"/>
       <c r="BD8" s="3"/>
       <c r="BE8" s="4"/>
@@ -1601,36 +1596,36 @@
         <v>5</v>
       </c>
       <c r="CO8" s="1"/>
-      <c r="CP8" s="7"/>
+      <c r="CP8" s="6"/>
       <c r="CQ8" s="1"/>
-      <c r="CR8" s="7"/>
+      <c r="CR8" s="6"/>
       <c r="CS8" s="1"/>
-      <c r="CT8" s="7"/>
+      <c r="CT8" s="6"/>
       <c r="CU8" s="1"/>
-      <c r="CV8" s="7"/>
+      <c r="CV8" s="6"/>
       <c r="CW8" s="1"/>
-      <c r="CX8" s="7"/>
+      <c r="CX8" s="6"/>
       <c r="CY8" s="1"/>
-      <c r="CZ8" s="7"/>
+      <c r="CZ8" s="6"/>
       <c r="DA8" s="1"/>
-      <c r="DB8" s="7"/>
+      <c r="DB8" s="6"/>
       <c r="DC8" s="1"/>
-      <c r="DD8" s="7"/>
+      <c r="DD8" s="6"/>
       <c r="DE8" s="1"/>
-      <c r="DF8" s="7"/>
+      <c r="DF8" s="6"/>
       <c r="DG8" s="1"/>
-      <c r="DH8" s="7"/>
+      <c r="DH8" s="6"/>
       <c r="DI8" s="1"/>
-      <c r="DJ8" s="7"/>
+      <c r="DJ8" s="6"/>
       <c r="DK8" s="1"/>
-      <c r="DL8" s="7"/>
+      <c r="DL8" s="6"/>
       <c r="DM8" s="1"/>
-      <c r="DN8" s="7"/>
+      <c r="DN8" s="6"/>
       <c r="DO8">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B9">
         <v>6</v>
       </c>
@@ -1670,7 +1665,7 @@
       <c r="AH9" s="4"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="2"/>
-      <c r="AK9" s="7"/>
+      <c r="AK9" s="6"/>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
       <c r="AN9" s="1"/>
@@ -1687,7 +1682,7 @@
       <c r="AY9" s="1"/>
       <c r="AZ9" s="1"/>
       <c r="BA9" s="1"/>
-      <c r="BB9" s="7"/>
+      <c r="BB9" s="6"/>
       <c r="BC9" s="2"/>
       <c r="BD9" s="3"/>
       <c r="BE9" s="4"/>
@@ -1760,7 +1755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B10">
         <v>7</v>
       </c>
@@ -1800,7 +1795,7 @@
       <c r="AH10" s="4"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="2"/>
-      <c r="AK10" s="7"/>
+      <c r="AK10" s="6"/>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
       <c r="AN10" s="1"/>
@@ -1817,7 +1812,7 @@
       <c r="AY10" s="1"/>
       <c r="AZ10" s="1"/>
       <c r="BA10" s="1"/>
-      <c r="BB10" s="7"/>
+      <c r="BB10" s="6"/>
       <c r="BC10" s="2"/>
       <c r="BD10" s="3"/>
       <c r="BE10" s="4"/>
@@ -1861,36 +1856,36 @@
         <v>7</v>
       </c>
       <c r="CO10" s="1"/>
-      <c r="CP10" s="7"/>
+      <c r="CP10" s="6"/>
       <c r="CQ10" s="1"/>
-      <c r="CR10" s="7"/>
+      <c r="CR10" s="6"/>
       <c r="CS10" s="1"/>
-      <c r="CT10" s="7"/>
+      <c r="CT10" s="6"/>
       <c r="CU10" s="1"/>
-      <c r="CV10" s="7"/>
+      <c r="CV10" s="6"/>
       <c r="CW10" s="1"/>
-      <c r="CX10" s="7"/>
+      <c r="CX10" s="6"/>
       <c r="CY10" s="1"/>
-      <c r="CZ10" s="7"/>
+      <c r="CZ10" s="6"/>
       <c r="DA10" s="1"/>
-      <c r="DB10" s="7"/>
+      <c r="DB10" s="6"/>
       <c r="DC10" s="1"/>
-      <c r="DD10" s="7"/>
+      <c r="DD10" s="6"/>
       <c r="DE10" s="1"/>
-      <c r="DF10" s="7"/>
+      <c r="DF10" s="6"/>
       <c r="DG10" s="1"/>
-      <c r="DH10" s="7"/>
+      <c r="DH10" s="6"/>
       <c r="DI10" s="1"/>
-      <c r="DJ10" s="7"/>
+      <c r="DJ10" s="6"/>
       <c r="DK10" s="1"/>
-      <c r="DL10" s="7"/>
+      <c r="DL10" s="6"/>
       <c r="DM10" s="1"/>
-      <c r="DN10" s="7"/>
+      <c r="DN10" s="6"/>
       <c r="DO10">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B11">
         <v>8</v>
       </c>
@@ -1930,7 +1925,7 @@
       <c r="AH11" s="4"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="2"/>
-      <c r="AK11" s="7"/>
+      <c r="AK11" s="6"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
@@ -1947,7 +1942,7 @@
       <c r="AY11" s="1"/>
       <c r="AZ11" s="1"/>
       <c r="BA11" s="1"/>
-      <c r="BB11" s="7"/>
+      <c r="BB11" s="6"/>
       <c r="BC11" s="2"/>
       <c r="BD11" s="3"/>
       <c r="BE11" s="4"/>
@@ -2020,7 +2015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B12">
         <v>9</v>
       </c>
@@ -2060,7 +2055,7 @@
       <c r="AH12" s="4"/>
       <c r="AI12" s="3"/>
       <c r="AJ12" s="2"/>
-      <c r="AK12" s="7"/>
+      <c r="AK12" s="6"/>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
       <c r="AN12" s="1"/>
@@ -2077,7 +2072,7 @@
       <c r="AY12" s="1"/>
       <c r="AZ12" s="1"/>
       <c r="BA12" s="1"/>
-      <c r="BB12" s="7"/>
+      <c r="BB12" s="6"/>
       <c r="BC12" s="2"/>
       <c r="BD12" s="3"/>
       <c r="BE12" s="4"/>
@@ -2121,36 +2116,36 @@
         <v>9</v>
       </c>
       <c r="CO12" s="1"/>
-      <c r="CP12" s="7"/>
+      <c r="CP12" s="6"/>
       <c r="CQ12" s="1"/>
-      <c r="CR12" s="7"/>
+      <c r="CR12" s="6"/>
       <c r="CS12" s="1"/>
-      <c r="CT12" s="7"/>
+      <c r="CT12" s="6"/>
       <c r="CU12" s="1"/>
-      <c r="CV12" s="7"/>
+      <c r="CV12" s="6"/>
       <c r="CW12" s="1"/>
-      <c r="CX12" s="7"/>
+      <c r="CX12" s="6"/>
       <c r="CY12" s="1"/>
-      <c r="CZ12" s="7"/>
+      <c r="CZ12" s="6"/>
       <c r="DA12" s="1"/>
-      <c r="DB12" s="7"/>
+      <c r="DB12" s="6"/>
       <c r="DC12" s="1"/>
-      <c r="DD12" s="7"/>
+      <c r="DD12" s="6"/>
       <c r="DE12" s="1"/>
-      <c r="DF12" s="7"/>
+      <c r="DF12" s="6"/>
       <c r="DG12" s="1"/>
-      <c r="DH12" s="7"/>
+      <c r="DH12" s="6"/>
       <c r="DI12" s="1"/>
-      <c r="DJ12" s="7"/>
+      <c r="DJ12" s="6"/>
       <c r="DK12" s="1"/>
-      <c r="DL12" s="7"/>
+      <c r="DL12" s="6"/>
       <c r="DM12" s="1"/>
-      <c r="DN12" s="7"/>
+      <c r="DN12" s="6"/>
       <c r="DO12">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B13">
         <v>10</v>
       </c>
@@ -2190,7 +2185,7 @@
       <c r="AH13" s="4"/>
       <c r="AI13" s="3"/>
       <c r="AJ13" s="2"/>
-      <c r="AK13" s="7"/>
+      <c r="AK13" s="6"/>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
@@ -2207,7 +2202,7 @@
       <c r="AY13" s="1"/>
       <c r="AZ13" s="1"/>
       <c r="BA13" s="1"/>
-      <c r="BB13" s="7"/>
+      <c r="BB13" s="6"/>
       <c r="BC13" s="2"/>
       <c r="BD13" s="3"/>
       <c r="BE13" s="4"/>
@@ -2280,7 +2275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B14">
         <v>11</v>
       </c>
@@ -2320,7 +2315,7 @@
       <c r="AH14" s="4"/>
       <c r="AI14" s="3"/>
       <c r="AJ14" s="2"/>
-      <c r="AK14" s="7"/>
+      <c r="AK14" s="6"/>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
       <c r="AN14" s="1"/>
@@ -2337,7 +2332,7 @@
       <c r="AY14" s="1"/>
       <c r="AZ14" s="1"/>
       <c r="BA14" s="1"/>
-      <c r="BB14" s="7"/>
+      <c r="BB14" s="6"/>
       <c r="BC14" s="2"/>
       <c r="BD14" s="3"/>
       <c r="BE14" s="4"/>
@@ -2381,36 +2376,36 @@
         <v>11</v>
       </c>
       <c r="CO14" s="1"/>
-      <c r="CP14" s="7"/>
+      <c r="CP14" s="6"/>
       <c r="CQ14" s="1"/>
-      <c r="CR14" s="7"/>
+      <c r="CR14" s="6"/>
       <c r="CS14" s="1"/>
-      <c r="CT14" s="7"/>
+      <c r="CT14" s="6"/>
       <c r="CU14" s="1"/>
-      <c r="CV14" s="7"/>
+      <c r="CV14" s="6"/>
       <c r="CW14" s="1"/>
-      <c r="CX14" s="7"/>
+      <c r="CX14" s="6"/>
       <c r="CY14" s="1"/>
-      <c r="CZ14" s="7"/>
+      <c r="CZ14" s="6"/>
       <c r="DA14" s="1"/>
-      <c r="DB14" s="7"/>
+      <c r="DB14" s="6"/>
       <c r="DC14" s="1"/>
-      <c r="DD14" s="7"/>
+      <c r="DD14" s="6"/>
       <c r="DE14" s="1"/>
-      <c r="DF14" s="7"/>
+      <c r="DF14" s="6"/>
       <c r="DG14" s="1"/>
-      <c r="DH14" s="7"/>
+      <c r="DH14" s="6"/>
       <c r="DI14" s="1"/>
-      <c r="DJ14" s="7"/>
+      <c r="DJ14" s="6"/>
       <c r="DK14" s="1"/>
-      <c r="DL14" s="7"/>
+      <c r="DL14" s="6"/>
       <c r="DM14" s="1"/>
-      <c r="DN14" s="7"/>
+      <c r="DN14" s="6"/>
       <c r="DO14">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B15">
         <v>12</v>
       </c>
@@ -2426,8 +2421,8 @@
       <c r="L15" s="4"/>
       <c r="M15" s="3"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="3"/>
       <c r="S15" s="4"/>
@@ -2450,7 +2445,7 @@
       <c r="AH15" s="4"/>
       <c r="AI15" s="3"/>
       <c r="AJ15" s="2"/>
-      <c r="AK15" s="7"/>
+      <c r="AK15" s="6"/>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
       <c r="AN15" s="1"/>
@@ -2467,7 +2462,7 @@
       <c r="AY15" s="1"/>
       <c r="AZ15" s="1"/>
       <c r="BA15" s="1"/>
-      <c r="BB15" s="7"/>
+      <c r="BB15" s="6"/>
       <c r="BC15" s="2"/>
       <c r="BD15" s="3"/>
       <c r="BE15" s="4"/>
@@ -2540,7 +2535,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B16">
         <v>13</v>
       </c>
@@ -2556,8 +2551,8 @@
       <c r="L16" s="4"/>
       <c r="M16" s="3"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="3"/>
       <c r="S16" s="4"/>
@@ -2580,7 +2575,7 @@
       <c r="AH16" s="4"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="2"/>
-      <c r="AK16" s="7"/>
+      <c r="AK16" s="6"/>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1"/>
@@ -2597,7 +2592,7 @@
       <c r="AY16" s="1"/>
       <c r="AZ16" s="1"/>
       <c r="BA16" s="1"/>
-      <c r="BB16" s="7"/>
+      <c r="BB16" s="6"/>
       <c r="BC16" s="2"/>
       <c r="BD16" s="3"/>
       <c r="BE16" s="4"/>
@@ -2621,7 +2616,7 @@
       <c r="BU16" s="4"/>
       <c r="BV16" s="3"/>
       <c r="BW16" s="2"/>
-      <c r="BX16" s="7"/>
+      <c r="BX16" s="6"/>
       <c r="BY16" s="2"/>
       <c r="BZ16" s="3"/>
       <c r="CA16" s="4"/>
@@ -2641,36 +2636,36 @@
         <v>13</v>
       </c>
       <c r="CO16" s="1"/>
-      <c r="CP16" s="7"/>
+      <c r="CP16" s="6"/>
       <c r="CQ16" s="1"/>
-      <c r="CR16" s="7"/>
+      <c r="CR16" s="6"/>
       <c r="CS16" s="1"/>
-      <c r="CT16" s="7"/>
+      <c r="CT16" s="6"/>
       <c r="CU16" s="1"/>
-      <c r="CV16" s="7"/>
+      <c r="CV16" s="6"/>
       <c r="CW16" s="1"/>
-      <c r="CX16" s="7"/>
+      <c r="CX16" s="6"/>
       <c r="CY16" s="1"/>
-      <c r="CZ16" s="7"/>
+      <c r="CZ16" s="6"/>
       <c r="DA16" s="1"/>
-      <c r="DB16" s="7"/>
+      <c r="DB16" s="6"/>
       <c r="DC16" s="1"/>
-      <c r="DD16" s="7"/>
+      <c r="DD16" s="6"/>
       <c r="DE16" s="1"/>
-      <c r="DF16" s="7"/>
+      <c r="DF16" s="6"/>
       <c r="DG16" s="1"/>
-      <c r="DH16" s="7"/>
+      <c r="DH16" s="6"/>
       <c r="DI16" s="1"/>
-      <c r="DJ16" s="7"/>
+      <c r="DJ16" s="6"/>
       <c r="DK16" s="1"/>
-      <c r="DL16" s="7"/>
+      <c r="DL16" s="6"/>
       <c r="DM16" s="1"/>
-      <c r="DN16" s="7"/>
+      <c r="DN16" s="6"/>
       <c r="DO16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B17">
         <v>14</v>
       </c>
@@ -2710,7 +2705,7 @@
       <c r="AH17" s="4"/>
       <c r="AI17" s="3"/>
       <c r="AJ17" s="2"/>
-      <c r="AK17" s="7"/>
+      <c r="AK17" s="6"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
@@ -2727,7 +2722,7 @@
       <c r="AY17" s="1"/>
       <c r="AZ17" s="1"/>
       <c r="BA17" s="1"/>
-      <c r="BB17" s="7"/>
+      <c r="BB17" s="6"/>
       <c r="BC17" s="2"/>
       <c r="BD17" s="3"/>
       <c r="BE17" s="4"/>
@@ -2800,7 +2795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B18">
         <v>15</v>
       </c>
@@ -2840,7 +2835,7 @@
       <c r="AH18" s="4"/>
       <c r="AI18" s="3"/>
       <c r="AJ18" s="2"/>
-      <c r="AK18" s="7"/>
+      <c r="AK18" s="6"/>
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
       <c r="AN18" s="1"/>
@@ -2857,7 +2852,7 @@
       <c r="AY18" s="1"/>
       <c r="AZ18" s="1"/>
       <c r="BA18" s="1"/>
-      <c r="BB18" s="7"/>
+      <c r="BB18" s="6"/>
       <c r="BC18" s="2"/>
       <c r="BD18" s="3"/>
       <c r="BE18" s="4"/>
@@ -2901,36 +2896,36 @@
         <v>15</v>
       </c>
       <c r="CO18" s="1"/>
-      <c r="CP18" s="7"/>
+      <c r="CP18" s="6"/>
       <c r="CQ18" s="1"/>
-      <c r="CR18" s="7"/>
+      <c r="CR18" s="6"/>
       <c r="CS18" s="1"/>
-      <c r="CT18" s="7"/>
+      <c r="CT18" s="6"/>
       <c r="CU18" s="1"/>
-      <c r="CV18" s="7"/>
+      <c r="CV18" s="6"/>
       <c r="CW18" s="1"/>
-      <c r="CX18" s="7"/>
+      <c r="CX18" s="6"/>
       <c r="CY18" s="1"/>
-      <c r="CZ18" s="7"/>
+      <c r="CZ18" s="6"/>
       <c r="DA18" s="1"/>
-      <c r="DB18" s="7"/>
+      <c r="DB18" s="6"/>
       <c r="DC18" s="1"/>
-      <c r="DD18" s="7"/>
+      <c r="DD18" s="6"/>
       <c r="DE18" s="1"/>
-      <c r="DF18" s="7"/>
+      <c r="DF18" s="6"/>
       <c r="DG18" s="1"/>
-      <c r="DH18" s="7"/>
+      <c r="DH18" s="6"/>
       <c r="DI18" s="1"/>
-      <c r="DJ18" s="7"/>
+      <c r="DJ18" s="6"/>
       <c r="DK18" s="1"/>
-      <c r="DL18" s="7"/>
+      <c r="DL18" s="6"/>
       <c r="DM18" s="1"/>
-      <c r="DN18" s="7"/>
+      <c r="DN18" s="6"/>
       <c r="DO18">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B19">
         <v>16</v>
       </c>
@@ -2970,7 +2965,7 @@
       <c r="AH19" s="4"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="2"/>
-      <c r="AK19" s="7"/>
+      <c r="AK19" s="6"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
@@ -2987,7 +2982,7 @@
       <c r="AY19" s="1"/>
       <c r="AZ19" s="1"/>
       <c r="BA19" s="1"/>
-      <c r="BB19" s="7"/>
+      <c r="BB19" s="6"/>
       <c r="BC19" s="2"/>
       <c r="BD19" s="3"/>
       <c r="BE19" s="4"/>
@@ -3060,7 +3055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B20">
         <v>17</v>
       </c>
@@ -3100,7 +3095,7 @@
       <c r="AH20" s="4"/>
       <c r="AI20" s="3"/>
       <c r="AJ20" s="2"/>
-      <c r="AK20" s="7"/>
+      <c r="AK20" s="6"/>
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1"/>
@@ -3117,7 +3112,7 @@
       <c r="AY20" s="1"/>
       <c r="AZ20" s="1"/>
       <c r="BA20" s="1"/>
-      <c r="BB20" s="7"/>
+      <c r="BB20" s="6"/>
       <c r="BC20" s="2"/>
       <c r="BD20" s="3"/>
       <c r="BE20" s="4"/>
@@ -3161,36 +3156,36 @@
         <v>17</v>
       </c>
       <c r="CO20" s="1"/>
-      <c r="CP20" s="7"/>
+      <c r="CP20" s="6"/>
       <c r="CQ20" s="1"/>
-      <c r="CR20" s="7"/>
+      <c r="CR20" s="6"/>
       <c r="CS20" s="1"/>
-      <c r="CT20" s="7"/>
+      <c r="CT20" s="6"/>
       <c r="CU20" s="1"/>
-      <c r="CV20" s="7"/>
+      <c r="CV20" s="6"/>
       <c r="CW20" s="1"/>
-      <c r="CX20" s="7"/>
+      <c r="CX20" s="6"/>
       <c r="CY20" s="1"/>
-      <c r="CZ20" s="7"/>
+      <c r="CZ20" s="6"/>
       <c r="DA20" s="1"/>
-      <c r="DB20" s="7"/>
+      <c r="DB20" s="6"/>
       <c r="DC20" s="1"/>
-      <c r="DD20" s="7"/>
+      <c r="DD20" s="6"/>
       <c r="DE20" s="1"/>
-      <c r="DF20" s="7"/>
+      <c r="DF20" s="6"/>
       <c r="DG20" s="1"/>
-      <c r="DH20" s="7"/>
+      <c r="DH20" s="6"/>
       <c r="DI20" s="1"/>
-      <c r="DJ20" s="7"/>
+      <c r="DJ20" s="6"/>
       <c r="DK20" s="1"/>
-      <c r="DL20" s="7"/>
+      <c r="DL20" s="6"/>
       <c r="DM20" s="1"/>
-      <c r="DN20" s="7"/>
+      <c r="DN20" s="6"/>
       <c r="DO20">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B21">
         <v>18</v>
       </c>
@@ -3230,7 +3225,7 @@
       <c r="AH21" s="4"/>
       <c r="AI21" s="3"/>
       <c r="AJ21" s="2"/>
-      <c r="AK21" s="7"/>
+      <c r="AK21" s="6"/>
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
       <c r="AN21" s="1"/>
@@ -3247,7 +3242,7 @@
       <c r="AY21" s="1"/>
       <c r="AZ21" s="1"/>
       <c r="BA21" s="1"/>
-      <c r="BB21" s="7"/>
+      <c r="BB21" s="6"/>
       <c r="BC21" s="2"/>
       <c r="BD21" s="3"/>
       <c r="BE21" s="4"/>
@@ -3320,7 +3315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B22">
         <v>19</v>
       </c>
@@ -3360,7 +3355,7 @@
       <c r="AH22" s="4"/>
       <c r="AI22" s="3"/>
       <c r="AJ22" s="2"/>
-      <c r="AK22" s="7"/>
+      <c r="AK22" s="6"/>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
       <c r="AN22" s="1"/>
@@ -3377,7 +3372,7 @@
       <c r="AY22" s="1"/>
       <c r="AZ22" s="1"/>
       <c r="BA22" s="1"/>
-      <c r="BB22" s="7"/>
+      <c r="BB22" s="6"/>
       <c r="BC22" s="2"/>
       <c r="BD22" s="3"/>
       <c r="BE22" s="4"/>
@@ -3421,36 +3416,36 @@
         <v>19</v>
       </c>
       <c r="CO22" s="1"/>
-      <c r="CP22" s="7"/>
+      <c r="CP22" s="6"/>
       <c r="CQ22" s="1"/>
-      <c r="CR22" s="7"/>
+      <c r="CR22" s="6"/>
       <c r="CS22" s="1"/>
-      <c r="CT22" s="7"/>
+      <c r="CT22" s="6"/>
       <c r="CU22" s="1"/>
-      <c r="CV22" s="7"/>
+      <c r="CV22" s="6"/>
       <c r="CW22" s="1"/>
-      <c r="CX22" s="7"/>
+      <c r="CX22" s="6"/>
       <c r="CY22" s="1"/>
-      <c r="CZ22" s="7"/>
+      <c r="CZ22" s="6"/>
       <c r="DA22" s="1"/>
-      <c r="DB22" s="7"/>
+      <c r="DB22" s="6"/>
       <c r="DC22" s="1"/>
-      <c r="DD22" s="7"/>
+      <c r="DD22" s="6"/>
       <c r="DE22" s="1"/>
-      <c r="DF22" s="7"/>
+      <c r="DF22" s="6"/>
       <c r="DG22" s="1"/>
-      <c r="DH22" s="7"/>
+      <c r="DH22" s="6"/>
       <c r="DI22" s="1"/>
-      <c r="DJ22" s="7"/>
+      <c r="DJ22" s="6"/>
       <c r="DK22" s="1"/>
-      <c r="DL22" s="7"/>
+      <c r="DL22" s="6"/>
       <c r="DM22" s="1"/>
-      <c r="DN22" s="7"/>
+      <c r="DN22" s="6"/>
       <c r="DO22">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B23">
         <v>20</v>
       </c>
@@ -3490,7 +3485,7 @@
       <c r="AH23" s="4"/>
       <c r="AI23" s="3"/>
       <c r="AJ23" s="2"/>
-      <c r="AK23" s="7"/>
+      <c r="AK23" s="6"/>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
       <c r="AN23" s="1"/>
@@ -3507,7 +3502,7 @@
       <c r="AY23" s="1"/>
       <c r="AZ23" s="1"/>
       <c r="BA23" s="1"/>
-      <c r="BB23" s="7"/>
+      <c r="BB23" s="6"/>
       <c r="BC23" s="2"/>
       <c r="BD23" s="3"/>
       <c r="BE23" s="4"/>
@@ -3580,7 +3575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B24">
         <v>21</v>
       </c>
@@ -3620,24 +3615,24 @@
       <c r="AH24" s="4"/>
       <c r="AI24" s="3"/>
       <c r="AJ24" s="2"/>
-      <c r="AK24" s="7"/>
-      <c r="AL24" s="7"/>
-      <c r="AM24" s="7"/>
-      <c r="AN24" s="7"/>
-      <c r="AO24" s="7"/>
-      <c r="AP24" s="7"/>
-      <c r="AQ24" s="7"/>
-      <c r="AR24" s="7"/>
-      <c r="AS24" s="7"/>
-      <c r="AT24" s="7"/>
-      <c r="AU24" s="7"/>
-      <c r="AV24" s="7"/>
-      <c r="AW24" s="7"/>
-      <c r="AX24" s="7"/>
-      <c r="AY24" s="7"/>
-      <c r="AZ24" s="7"/>
-      <c r="BA24" s="7"/>
-      <c r="BB24" s="7"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="6"/>
+      <c r="AN24" s="6"/>
+      <c r="AO24" s="6"/>
+      <c r="AP24" s="6"/>
+      <c r="AQ24" s="6"/>
+      <c r="AR24" s="6"/>
+      <c r="AS24" s="6"/>
+      <c r="AT24" s="6"/>
+      <c r="AU24" s="6"/>
+      <c r="AV24" s="6"/>
+      <c r="AW24" s="6"/>
+      <c r="AX24" s="6"/>
+      <c r="AY24" s="6"/>
+      <c r="AZ24" s="6"/>
+      <c r="BA24" s="6"/>
+      <c r="BB24" s="6"/>
       <c r="BC24" s="2"/>
       <c r="BD24" s="3"/>
       <c r="BE24" s="4"/>
@@ -3681,36 +3676,36 @@
         <v>21</v>
       </c>
       <c r="CO24" s="1"/>
-      <c r="CP24" s="7"/>
+      <c r="CP24" s="6"/>
       <c r="CQ24" s="1"/>
-      <c r="CR24" s="7"/>
+      <c r="CR24" s="6"/>
       <c r="CS24" s="1"/>
-      <c r="CT24" s="7"/>
+      <c r="CT24" s="6"/>
       <c r="CU24" s="1"/>
-      <c r="CV24" s="7"/>
+      <c r="CV24" s="6"/>
       <c r="CW24" s="1"/>
-      <c r="CX24" s="7"/>
+      <c r="CX24" s="6"/>
       <c r="CY24" s="1"/>
-      <c r="CZ24" s="7"/>
+      <c r="CZ24" s="6"/>
       <c r="DA24" s="1"/>
-      <c r="DB24" s="7"/>
+      <c r="DB24" s="6"/>
       <c r="DC24" s="1"/>
-      <c r="DD24" s="7"/>
+      <c r="DD24" s="6"/>
       <c r="DE24" s="1"/>
-      <c r="DF24" s="7"/>
+      <c r="DF24" s="6"/>
       <c r="DG24" s="1"/>
-      <c r="DH24" s="7"/>
+      <c r="DH24" s="6"/>
       <c r="DI24" s="1"/>
-      <c r="DJ24" s="7"/>
+      <c r="DJ24" s="6"/>
       <c r="DK24" s="1"/>
-      <c r="DL24" s="7"/>
+      <c r="DL24" s="6"/>
       <c r="DM24" s="1"/>
-      <c r="DN24" s="7"/>
+      <c r="DN24" s="6"/>
       <c r="DO24">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B25">
         <v>22</v>
       </c>
@@ -3840,7 +3835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B26">
         <v>23</v>
       </c>
@@ -3941,36 +3936,36 @@
         <v>23</v>
       </c>
       <c r="CO26" s="1"/>
-      <c r="CP26" s="7"/>
+      <c r="CP26" s="6"/>
       <c r="CQ26" s="1"/>
-      <c r="CR26" s="7"/>
+      <c r="CR26" s="6"/>
       <c r="CS26" s="1"/>
-      <c r="CT26" s="7"/>
+      <c r="CT26" s="6"/>
       <c r="CU26" s="1"/>
-      <c r="CV26" s="7"/>
+      <c r="CV26" s="6"/>
       <c r="CW26" s="1"/>
-      <c r="CX26" s="7"/>
+      <c r="CX26" s="6"/>
       <c r="CY26" s="1"/>
-      <c r="CZ26" s="7"/>
+      <c r="CZ26" s="6"/>
       <c r="DA26" s="1"/>
-      <c r="DB26" s="7"/>
+      <c r="DB26" s="6"/>
       <c r="DC26" s="1"/>
-      <c r="DD26" s="7"/>
+      <c r="DD26" s="6"/>
       <c r="DE26" s="1"/>
-      <c r="DF26" s="7"/>
+      <c r="DF26" s="6"/>
       <c r="DG26" s="1"/>
-      <c r="DH26" s="7"/>
+      <c r="DH26" s="6"/>
       <c r="DI26" s="1"/>
-      <c r="DJ26" s="7"/>
+      <c r="DJ26" s="6"/>
       <c r="DK26" s="1"/>
-      <c r="DL26" s="7"/>
+      <c r="DL26" s="6"/>
       <c r="DM26" s="1"/>
-      <c r="DN26" s="7"/>
+      <c r="DN26" s="6"/>
       <c r="DO26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B27">
         <v>24</v>
       </c>
@@ -4100,7 +4095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B28">
         <v>25</v>
       </c>
@@ -4201,36 +4196,36 @@
         <v>25</v>
       </c>
       <c r="CO28" s="1"/>
-      <c r="CP28" s="7"/>
+      <c r="CP28" s="6"/>
       <c r="CQ28" s="1"/>
-      <c r="CR28" s="7"/>
+      <c r="CR28" s="6"/>
       <c r="CS28" s="1"/>
-      <c r="CT28" s="7"/>
+      <c r="CT28" s="6"/>
       <c r="CU28" s="1"/>
-      <c r="CV28" s="7"/>
+      <c r="CV28" s="6"/>
       <c r="CW28" s="1"/>
-      <c r="CX28" s="7"/>
+      <c r="CX28" s="6"/>
       <c r="CY28" s="1"/>
-      <c r="CZ28" s="7"/>
+      <c r="CZ28" s="6"/>
       <c r="DA28" s="1"/>
-      <c r="DB28" s="7"/>
+      <c r="DB28" s="6"/>
       <c r="DC28" s="1"/>
-      <c r="DD28" s="7"/>
+      <c r="DD28" s="6"/>
       <c r="DE28" s="1"/>
-      <c r="DF28" s="7"/>
+      <c r="DF28" s="6"/>
       <c r="DG28" s="1"/>
-      <c r="DH28" s="7"/>
+      <c r="DH28" s="6"/>
       <c r="DI28" s="1"/>
-      <c r="DJ28" s="7"/>
+      <c r="DJ28" s="6"/>
       <c r="DK28" s="1"/>
-      <c r="DL28" s="7"/>
+      <c r="DL28" s="6"/>
       <c r="DM28" s="1"/>
-      <c r="DN28" s="7"/>
+      <c r="DN28" s="6"/>
       <c r="DO28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:119" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:119" x14ac:dyDescent="0.45">
       <c r="C29">
         <v>25</v>
       </c>
@@ -4309,7 +4304,6 @@
       <c r="AB29">
         <v>0</v>
       </c>
-      <c r="AF29"/>
       <c r="AG29">
         <v>25</v>
       </c>
@@ -4388,7 +4382,6 @@
       <c r="BF29">
         <v>0</v>
       </c>
-      <c r="BJ29"/>
       <c r="BK29">
         <v>25</v>
       </c>
@@ -4467,8 +4460,6 @@
       <c r="CJ29">
         <v>0</v>
       </c>
-      <c r="CK29"/>
-      <c r="CN29"/>
       <c r="CO29">
         <v>25</v>
       </c>
@@ -4547,11 +4538,9 @@
       <c r="DN29">
         <v>0</v>
       </c>
-      <c r="DO29"/>
     </row>
-    <row r="30" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="31" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="B31" s="6" t="s">
+    <row r="31" spans="2:119" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
         <v>0</v>
       </c>
       <c r="C31">
@@ -4632,8 +4621,7 @@
       <c r="AB31">
         <v>25</v>
       </c>
-      <c r="AC31"/>
-      <c r="AF31" s="6" t="s">
+      <c r="AF31" t="s">
         <v>0</v>
       </c>
       <c r="AG31">
@@ -4714,8 +4702,7 @@
       <c r="BF31">
         <v>25</v>
       </c>
-      <c r="BG31"/>
-      <c r="BJ31" s="6" t="s">
+      <c r="BJ31" t="s">
         <v>0</v>
       </c>
       <c r="BK31">
@@ -4796,8 +4783,7 @@
       <c r="CJ31">
         <v>25</v>
       </c>
-      <c r="CK31"/>
-      <c r="CN31" s="6" t="s">
+      <c r="CN31" t="s">
         <v>0</v>
       </c>
       <c r="CO31">
@@ -4878,9 +4864,8 @@
       <c r="DN31">
         <v>25</v>
       </c>
-      <c r="DO31"/>
     </row>
-    <row r="32" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B32">
         <v>0</v>
       </c>
@@ -5010,7 +4995,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B33">
         <v>1</v>
       </c>
@@ -5140,7 +5125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>2</v>
       </c>
@@ -5270,7 +5255,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B35">
         <v>3</v>
       </c>
@@ -5400,7 +5385,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B36">
         <v>4</v>
       </c>
@@ -5530,7 +5515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B37">
         <v>5</v>
       </c>
@@ -5660,7 +5645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B38">
         <v>6</v>
       </c>
@@ -5790,7 +5775,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B39">
         <v>7</v>
       </c>
@@ -5920,7 +5905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B40">
         <v>8</v>
       </c>
@@ -6050,7 +6035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B41">
         <v>9</v>
       </c>
@@ -6180,7 +6165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B42">
         <v>10</v>
       </c>
@@ -6310,7 +6295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B43">
         <v>11</v>
       </c>
@@ -6440,7 +6425,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B44">
         <v>12</v>
       </c>
@@ -6570,7 +6555,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B45">
         <v>13</v>
       </c>
@@ -6700,7 +6685,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B46">
         <v>14</v>
       </c>
@@ -6830,7 +6815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B47">
         <v>15</v>
       </c>
@@ -6960,7 +6945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B48">
         <v>16</v>
       </c>
@@ -7090,7 +7075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B49">
         <v>17</v>
       </c>
@@ -7220,7 +7205,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="50" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B50">
         <v>18</v>
       </c>
@@ -7350,7 +7335,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B51">
         <v>19</v>
       </c>
@@ -7480,7 +7465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B52">
         <v>20</v>
       </c>
@@ -7610,7 +7595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B53">
         <v>21</v>
       </c>
@@ -7740,7 +7725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B54">
         <v>22</v>
       </c>
@@ -7870,7 +7855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B55">
         <v>23</v>
       </c>
@@ -8000,7 +7985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B56">
         <v>24</v>
       </c>
@@ -8130,7 +8115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:119" x14ac:dyDescent="0.45">
       <c r="B57">
         <v>25</v>
       </c>
@@ -8260,8 +8245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="B58"/>
+    <row r="58" spans="2:119" x14ac:dyDescent="0.45">
       <c r="C58">
         <v>25</v>
       </c>
@@ -8340,8 +8324,6 @@
       <c r="AB58">
         <v>0</v>
       </c>
-      <c r="AC58"/>
-      <c r="AF58"/>
       <c r="AG58">
         <v>25</v>
       </c>
@@ -8420,8 +8402,6 @@
       <c r="BF58">
         <v>0</v>
       </c>
-      <c r="BG58"/>
-      <c r="BJ58"/>
       <c r="BK58">
         <v>25</v>
       </c>
@@ -8500,8 +8480,6 @@
       <c r="CJ58">
         <v>0</v>
       </c>
-      <c r="CK58"/>
-      <c r="CN58"/>
       <c r="CO58">
         <v>25</v>
       </c>
@@ -8580,10 +8558,7 @@
       <c r="DN58">
         <v>0</v>
       </c>
-      <c r="DO58"/>
     </row>
-    <row r="59" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="60" spans="2:119" s="6" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
